--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/0.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/0.xlsx
@@ -426,13 +426,13 @@
         <v>4.827985509188549</v>
       </c>
       <c r="E2">
-        <v>-10.20218771289457</v>
+        <v>-10.01653916667473</v>
       </c>
       <c r="F2">
-        <v>-2.037075704004898</v>
+        <v>-3.277766295017469</v>
       </c>
       <c r="G2">
-        <v>-11.27227039667283</v>
+        <v>-10.41123377680071</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>4.036244641434841</v>
       </c>
       <c r="E3">
-        <v>-9.832061826048497</v>
+        <v>-10.04147920068033</v>
       </c>
       <c r="F3">
-        <v>-1.951333879243329</v>
+        <v>-3.369183264855617</v>
       </c>
       <c r="G3">
-        <v>-11.24186305442013</v>
+        <v>-10.1712201943059</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>3.21023863246733</v>
       </c>
       <c r="E4">
-        <v>-12.06948398417145</v>
+        <v>-10.35742229258268</v>
       </c>
       <c r="F4">
-        <v>-1.862518811417375</v>
+        <v>-3.1287910445632</v>
       </c>
       <c r="G4">
-        <v>-11.58109798510021</v>
+        <v>-10.24949423326436</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>2.473687965873329</v>
       </c>
       <c r="E5">
-        <v>-11.85884971862145</v>
+        <v>-11.18771153458578</v>
       </c>
       <c r="F5">
-        <v>-0.9925739919365566</v>
+        <v>-3.038379712752051</v>
       </c>
       <c r="G5">
-        <v>-10.90344398142478</v>
+        <v>-10.46895342359334</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>1.843384976137184</v>
       </c>
       <c r="E6">
-        <v>-11.91470625772907</v>
+        <v>-12.41161307347685</v>
       </c>
       <c r="F6">
-        <v>-1.224701590651242</v>
+        <v>-2.763396526453533</v>
       </c>
       <c r="G6">
-        <v>-10.72392135110606</v>
+        <v>-10.42762533671602</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>1.369653687621421</v>
       </c>
       <c r="E7">
-        <v>-13.29198173763474</v>
+        <v>-12.38364534841546</v>
       </c>
       <c r="F7">
-        <v>-1.753084022200935</v>
+        <v>-2.193654538849463</v>
       </c>
       <c r="G7">
-        <v>-11.56599482764062</v>
+        <v>-9.843180136432512</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>1.074893970766468</v>
       </c>
       <c r="E8">
-        <v>-13.45965933845204</v>
+        <v>-12.5280275869118</v>
       </c>
       <c r="F8">
-        <v>-1.548875718430204</v>
+        <v>-2.638854800912238</v>
       </c>
       <c r="G8">
-        <v>-11.89493559239794</v>
+        <v>-9.995609764756956</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>0.9792680909949977</v>
       </c>
       <c r="E9">
-        <v>-13.33765044936255</v>
+        <v>-13.19014084273861</v>
       </c>
       <c r="F9">
-        <v>-1.246684804786736</v>
+        <v>-1.932420594702611</v>
       </c>
       <c r="G9">
-        <v>-11.52250896035874</v>
+        <v>-9.898999161162809</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>1.083336947224778</v>
       </c>
       <c r="E10">
-        <v>-14.38045120843447</v>
+        <v>-13.40412259661643</v>
       </c>
       <c r="F10">
-        <v>-0.6650159833171593</v>
+        <v>-1.855818975863533</v>
       </c>
       <c r="G10">
-        <v>-9.808527723474665</v>
+        <v>-9.456286063241661</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>1.370675147719543</v>
       </c>
       <c r="E11">
-        <v>-13.27574268135466</v>
+        <v>-14.59583259452876</v>
       </c>
       <c r="F11">
-        <v>-0.5155453691560165</v>
+        <v>-1.637366066234261</v>
       </c>
       <c r="G11">
-        <v>-10.11499389341938</v>
+        <v>-9.608156992223607</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>1.809893020807832</v>
       </c>
       <c r="E12">
-        <v>-16.02496507103623</v>
+        <v>-15.27631550404529</v>
       </c>
       <c r="F12">
-        <v>-0.09898011147321507</v>
+        <v>-1.799799801881813</v>
       </c>
       <c r="G12">
-        <v>-9.181035261000588</v>
+        <v>-8.9988875269955</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>2.355042197511281</v>
       </c>
       <c r="E13">
-        <v>-15.57602369287889</v>
+        <v>-15.18929742036748</v>
       </c>
       <c r="F13">
-        <v>-0.1741751624623402</v>
+        <v>-1.599448376738516</v>
       </c>
       <c r="G13">
-        <v>-9.263083131265505</v>
+        <v>-8.595603199261639</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>2.955965654108996</v>
       </c>
       <c r="E14">
-        <v>-15.54560141992452</v>
+        <v>-16.26548999849103</v>
       </c>
       <c r="F14">
-        <v>0.1234986637336621</v>
+        <v>-1.173274057183241</v>
       </c>
       <c r="G14">
-        <v>-7.980223286318031</v>
+        <v>-8.317652887113354</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>3.560470140274848</v>
       </c>
       <c r="E15">
-        <v>-18.68294971433398</v>
+        <v>-17.33722202765171</v>
       </c>
       <c r="F15">
-        <v>-0.1499006840907035</v>
+        <v>-1.236613513903499</v>
       </c>
       <c r="G15">
-        <v>-9.00088213586311</v>
+        <v>-7.24298686958421</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>4.118093688392234</v>
       </c>
       <c r="E16">
-        <v>-16.87233647121835</v>
+        <v>-18.40011602311315</v>
       </c>
       <c r="F16">
-        <v>0.485611190193438</v>
+        <v>-0.8397990202056466</v>
       </c>
       <c r="G16">
-        <v>-7.960700138265686</v>
+        <v>-7.190706709147167</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>4.591012081314585</v>
       </c>
       <c r="E17">
-        <v>-18.88700113993413</v>
+        <v>-19.02870040391463</v>
       </c>
       <c r="F17">
-        <v>0.3554448499871349</v>
+        <v>-0.9016714382555472</v>
       </c>
       <c r="G17">
-        <v>-7.333399565519055</v>
+        <v>-6.998349658418531</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>4.94874879250504</v>
       </c>
       <c r="E18">
-        <v>-19.70905871709142</v>
+        <v>-19.58525148749828</v>
       </c>
       <c r="F18">
-        <v>0.7701802440771522</v>
+        <v>-0.08979186024136296</v>
       </c>
       <c r="G18">
-        <v>-6.597498544643589</v>
+        <v>-6.674084737223897</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>5.175257903604667</v>
       </c>
       <c r="E19">
-        <v>-20.66619533937743</v>
+        <v>-21.23665552768793</v>
       </c>
       <c r="F19">
-        <v>0.7965438650386493</v>
+        <v>-0.01346028917559692</v>
       </c>
       <c r="G19">
-        <v>-6.50468396368492</v>
+        <v>-6.385438204485821</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>5.264732109636071</v>
       </c>
       <c r="E20">
-        <v>-21.5110166678061</v>
+        <v>-21.03609279960063</v>
       </c>
       <c r="F20">
-        <v>0.9962267976878869</v>
+        <v>0.3377575492025598</v>
       </c>
       <c r="G20">
-        <v>-4.621621769474276</v>
+        <v>-5.545256212407517</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>5.222045502535762</v>
       </c>
       <c r="E21">
-        <v>-22.91353536614407</v>
+        <v>-21.68631541140446</v>
       </c>
       <c r="F21">
-        <v>0.878437923214214</v>
+        <v>0.4982984653347153</v>
       </c>
       <c r="G21">
-        <v>-6.287697148483722</v>
+        <v>-5.269994967188079</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>5.060361006017613</v>
       </c>
       <c r="E22">
-        <v>-21.38717205931104</v>
+        <v>-22.73196527344522</v>
       </c>
       <c r="F22">
-        <v>2.260954953994894</v>
+        <v>0.6186105469173154</v>
       </c>
       <c r="G22">
-        <v>-5.494046457252829</v>
+        <v>-5.494905392223306</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>4.798765035118844</v>
       </c>
       <c r="E23">
-        <v>-23.02226643862809</v>
+        <v>-22.86871806273785</v>
       </c>
       <c r="F23">
-        <v>1.94402655588822</v>
+        <v>1.059661516659467</v>
       </c>
       <c r="G23">
-        <v>-5.86668064348702</v>
+        <v>-5.484446749391306</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>4.460245589409827</v>
       </c>
       <c r="E24">
-        <v>-23.00106429481484</v>
+        <v>-24.00754522085114</v>
       </c>
       <c r="F24">
-        <v>2.099269234112069</v>
+        <v>1.065392162352034</v>
       </c>
       <c r="G24">
-        <v>-6.320349731084775</v>
+        <v>-5.548772885371746</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>4.068752079336385</v>
       </c>
       <c r="E25">
-        <v>-23.77186709101241</v>
+        <v>-24.15583978441546</v>
       </c>
       <c r="F25">
-        <v>1.649459107452715</v>
+        <v>1.323400443832385</v>
       </c>
       <c r="G25">
-        <v>-5.622187023273852</v>
+        <v>-5.321202111598175</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.649586086216887</v>
       </c>
       <c r="E26">
-        <v>-24.3512068451354</v>
+        <v>-23.80856071306728</v>
       </c>
       <c r="F26">
-        <v>2.215717810128013</v>
+        <v>1.358824747445703</v>
       </c>
       <c r="G26">
-        <v>-5.405111442756556</v>
+        <v>-5.891242528600213</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>3.224849376178061</v>
       </c>
       <c r="E27">
-        <v>-24.56988588102159</v>
+        <v>-24.38774679837124</v>
       </c>
       <c r="F27">
-        <v>1.923267668774064</v>
+        <v>1.364200851889872</v>
       </c>
       <c r="G27">
-        <v>-6.427082191458669</v>
+        <v>-6.09307658219459</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.818214970772076</v>
       </c>
       <c r="E28">
-        <v>-23.74430638066085</v>
+        <v>-23.43534068378421</v>
       </c>
       <c r="F28">
-        <v>1.92492937378408</v>
+        <v>1.660158300827274</v>
       </c>
       <c r="G28">
-        <v>-5.087201073896691</v>
+        <v>-6.124742303340204</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.446385484138824</v>
       </c>
       <c r="E29">
-        <v>-24.06538699497202</v>
+        <v>-23.89712379135792</v>
       </c>
       <c r="F29">
-        <v>2.128354870359165</v>
+        <v>1.083092717015054</v>
       </c>
       <c r="G29">
-        <v>-6.159305950981953</v>
+        <v>-6.139370305284212</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>2.129190789545127</v>
       </c>
       <c r="E30">
-        <v>-24.15388777509279</v>
+        <v>-23.4216724653142</v>
       </c>
       <c r="F30">
-        <v>1.556625629355781</v>
+        <v>0.758120871427197</v>
       </c>
       <c r="G30">
-        <v>-5.711310011380686</v>
+        <v>-6.306643321981431</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.880614783802723</v>
       </c>
       <c r="E31">
-        <v>-22.49421053794408</v>
+        <v>-22.38704937934086</v>
       </c>
       <c r="F31">
-        <v>2.000842619311432</v>
+        <v>1.045768138579714</v>
       </c>
       <c r="G31">
-        <v>-5.52730212185443</v>
+        <v>-6.157387053707484</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.712206602588035</v>
       </c>
       <c r="E32">
-        <v>-22.17678474959877</v>
+        <v>-22.7414138292092</v>
       </c>
       <c r="F32">
-        <v>1.355739907237678</v>
+        <v>0.9140891994958991</v>
       </c>
       <c r="G32">
-        <v>-5.848992848882228</v>
+        <v>-5.906807787852431</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.634531375669169</v>
       </c>
       <c r="E33">
-        <v>-22.29767642484187</v>
+        <v>-23.13586922799612</v>
       </c>
       <c r="F33">
-        <v>1.298512973582677</v>
+        <v>0.7725907932192988</v>
       </c>
       <c r="G33">
-        <v>-5.100779556515071</v>
+        <v>-6.113121879165158</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>1.650282658409187</v>
       </c>
       <c r="E34">
-        <v>-21.38546093624521</v>
+        <v>-22.16638926165272</v>
       </c>
       <c r="F34">
-        <v>1.103992426587686</v>
+        <v>1.135750376076213</v>
       </c>
       <c r="G34">
-        <v>-5.053778321641258</v>
+        <v>-5.96416584651919</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.761770979201705</v>
       </c>
       <c r="E35">
-        <v>-22.11569101101054</v>
+        <v>-21.81278069624549</v>
       </c>
       <c r="F35">
-        <v>2.103091321308586</v>
+        <v>0.6895900361935939</v>
       </c>
       <c r="G35">
-        <v>-5.87205094511094</v>
+        <v>-5.911522792583981</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.963301320357527</v>
       </c>
       <c r="E36">
-        <v>-22.14086362485032</v>
+        <v>-21.59995353511598</v>
       </c>
       <c r="F36">
-        <v>2.022047168088294</v>
+        <v>0.815571464280954</v>
       </c>
       <c r="G36">
-        <v>-5.749865487502247</v>
+        <v>-5.531199963528962</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>2.247573511479769</v>
       </c>
       <c r="E37">
-        <v>-20.7014519503139</v>
+        <v>-20.69123920366614</v>
       </c>
       <c r="F37">
-        <v>1.508282107728401</v>
+        <v>0.9460824053268216</v>
       </c>
       <c r="G37">
-        <v>-5.43621846455967</v>
+        <v>-5.748680209457881</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>2.604243646282413</v>
       </c>
       <c r="E38">
-        <v>-20.96314164268002</v>
+        <v>-20.48828007264442</v>
       </c>
       <c r="F38">
-        <v>1.253231097876045</v>
+        <v>0.8599305387008674</v>
       </c>
       <c r="G38">
-        <v>-4.962480583290026</v>
+        <v>-5.198935720907157</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>3.015802961642678</v>
       </c>
       <c r="E39">
-        <v>-20.18282799254858</v>
+        <v>-19.688263587988</v>
       </c>
       <c r="F39">
-        <v>1.852256701536479</v>
+        <v>0.716548424950301</v>
       </c>
       <c r="G39">
-        <v>-4.814273834341708</v>
+        <v>-4.910411893164863</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>3.469637121135668</v>
       </c>
       <c r="E40">
-        <v>-20.76508745423292</v>
+        <v>-19.49308757498901</v>
       </c>
       <c r="F40">
-        <v>2.082905664437168</v>
+        <v>0.9196243504814055</v>
       </c>
       <c r="G40">
-        <v>-5.035163712706621</v>
+        <v>-4.14442987311059</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>3.944824437387803</v>
       </c>
       <c r="E41">
-        <v>-17.7970448194801</v>
+        <v>-19.49037552799389</v>
       </c>
       <c r="F41">
-        <v>1.766886813738768</v>
+        <v>0.6041406251252137</v>
       </c>
       <c r="G41">
-        <v>-5.114629556570927</v>
+        <v>-4.347710279208443</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>4.424829616608593</v>
       </c>
       <c r="E42">
-        <v>-19.05224080570376</v>
+        <v>-18.96670541846891</v>
       </c>
       <c r="F42">
-        <v>2.329618328012945</v>
+        <v>0.8222149708514059</v>
       </c>
       <c r="G42">
-        <v>-3.917678873138628</v>
+        <v>-3.658089927699642</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>4.889264471687215</v>
       </c>
       <c r="E43">
-        <v>-17.49943400236554</v>
+        <v>-18.35992955033411</v>
       </c>
       <c r="F43">
-        <v>1.901267887290515</v>
+        <v>0.6609442630373842</v>
       </c>
       <c r="G43">
-        <v>-4.632900186107886</v>
+        <v>-3.967340456750784</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>5.318048853609339</v>
       </c>
       <c r="E44">
-        <v>-17.85329176045225</v>
+        <v>-18.61618268907603</v>
       </c>
       <c r="F44">
-        <v>2.00266171412798</v>
+        <v>0.6847573407656615</v>
       </c>
       <c r="G44">
-        <v>-4.576455888048016</v>
+        <v>-3.697608768575324</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>5.693502865292512</v>
       </c>
       <c r="E45">
-        <v>-18.63554080706106</v>
+        <v>-17.80943800207339</v>
       </c>
       <c r="F45">
-        <v>1.732380341207752</v>
+        <v>0.1249483066885613</v>
       </c>
       <c r="G45">
-        <v>-4.123327224580621</v>
+        <v>-3.296846420116479</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>5.996470498411016</v>
       </c>
       <c r="E46">
-        <v>-16.50767205726443</v>
+        <v>-17.76803048516485</v>
       </c>
       <c r="F46">
-        <v>1.674084813603139</v>
+        <v>0.2096919487297563</v>
       </c>
       <c r="G46">
-        <v>-2.892444693697622</v>
+        <v>-3.33948249003395</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>6.215254223368162</v>
       </c>
       <c r="E47">
-        <v>-16.56867442520351</v>
+        <v>-17.10712996704488</v>
       </c>
       <c r="F47">
-        <v>1.711565125110206</v>
+        <v>0.2844819280589125</v>
       </c>
       <c r="G47">
-        <v>-4.055178958518791</v>
+        <v>-3.298193564325494</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>6.337578920010982</v>
       </c>
       <c r="E48">
-        <v>-16.07627384374317</v>
+        <v>-15.90835950988035</v>
       </c>
       <c r="F48">
-        <v>1.510845076472663</v>
+        <v>0.2166320108304106</v>
       </c>
       <c r="G48">
-        <v>-3.209331650677771</v>
+        <v>-3.16861969952395</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>6.360658892441052</v>
       </c>
       <c r="E49">
-        <v>-15.9283239967188</v>
+        <v>-15.31476593449055</v>
       </c>
       <c r="F49">
-        <v>1.199269588522879</v>
+        <v>0.05488002155536229</v>
       </c>
       <c r="G49">
-        <v>-3.950428053289552</v>
+        <v>-3.295321745275269</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>6.283724161857705</v>
       </c>
       <c r="E50">
-        <v>-15.38064001931366</v>
+        <v>-14.94926672506034</v>
       </c>
       <c r="F50">
-        <v>1.514536281619538</v>
+        <v>-0.2850513109596512</v>
       </c>
       <c r="G50">
-        <v>-4.179922945826775</v>
+        <v>-3.229570142748081</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>6.114307754948761</v>
       </c>
       <c r="E51">
-        <v>-15.23354988703353</v>
+        <v>-14.2217777697694</v>
       </c>
       <c r="F51">
-        <v>1.3932367860928</v>
+        <v>-0.2967470303197774</v>
       </c>
       <c r="G51">
-        <v>-4.720738687875892</v>
+        <v>-2.59186966892275</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>5.861665655646855</v>
       </c>
       <c r="E52">
-        <v>-13.58619107467426</v>
+        <v>-14.30004088397447</v>
       </c>
       <c r="F52">
-        <v>1.417294232204904</v>
+        <v>-0.3662288313317944</v>
       </c>
       <c r="G52">
-        <v>-4.122395188761593</v>
+        <v>-2.966874411245671</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>5.543873041867667</v>
       </c>
       <c r="E53">
-        <v>-14.5196294731408</v>
+        <v>-13.41983834826958</v>
       </c>
       <c r="F53">
-        <v>1.338413774640723</v>
+        <v>-0.233857377099239</v>
       </c>
       <c r="G53">
-        <v>-4.24796678210496</v>
+        <v>-2.939438096337661</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>5.178124053392655</v>
       </c>
       <c r="E54">
-        <v>-13.85941423488943</v>
+        <v>-13.1232949064655</v>
       </c>
       <c r="F54">
-        <v>1.001853069087701</v>
+        <v>-0.4137746351502776</v>
       </c>
       <c r="G54">
-        <v>-3.397464516657985</v>
+        <v>-3.633428834291986</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>4.784880917802375</v>
       </c>
       <c r="E55">
-        <v>-12.58174522218713</v>
+        <v>-12.92388261791518</v>
       </c>
       <c r="F55">
-        <v>1.708263252642647</v>
+        <v>-0.3475607435423047</v>
       </c>
       <c r="G55">
-        <v>-3.777087666162586</v>
+        <v>-3.565066487173685</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>4.382892352241694</v>
       </c>
       <c r="E56">
-        <v>-13.50084673516036</v>
+        <v>-12.66497557713669</v>
       </c>
       <c r="F56">
-        <v>0.7411227723217512</v>
+        <v>-0.4836374851675823</v>
       </c>
       <c r="G56">
-        <v>-3.980185320139062</v>
+        <v>-3.591471557968204</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>3.988410734381003</v>
       </c>
       <c r="E57">
-        <v>-13.15144537282519</v>
+        <v>-12.19023860344084</v>
       </c>
       <c r="F57">
-        <v>0.9025003395307341</v>
+        <v>-0.611495993789686</v>
       </c>
       <c r="G57">
-        <v>-4.939083090264469</v>
+        <v>-3.478789210671164</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>3.616836910166317</v>
       </c>
       <c r="E58">
-        <v>-11.35300519210263</v>
+        <v>-12.14267602734891</v>
       </c>
       <c r="F58">
-        <v>1.062744700132687</v>
+        <v>-0.6131403030842431</v>
       </c>
       <c r="G58">
-        <v>-4.13326893998358</v>
+        <v>-3.964366818661506</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>3.273909371632314</v>
       </c>
       <c r="E59">
-        <v>-11.64151216999317</v>
+        <v>-11.17149739757365</v>
       </c>
       <c r="F59">
-        <v>1.011647685258402</v>
+        <v>-0.786441390689122</v>
       </c>
       <c r="G59">
-        <v>-4.67017378663521</v>
+        <v>-4.370076528120511</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>2.967963517391959</v>
       </c>
       <c r="E60">
-        <v>-12.79637487703162</v>
+        <v>-10.72388089382893</v>
       </c>
       <c r="F60">
-        <v>0.01997924614061352</v>
+        <v>-0.5712862116903952</v>
       </c>
       <c r="G60">
-        <v>-5.248338840804793</v>
+        <v>-3.84193856180584</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>2.695345393428214</v>
       </c>
       <c r="E61">
-        <v>-9.708885884576732</v>
+        <v>-10.7367890746265</v>
       </c>
       <c r="F61">
-        <v>0.9397188869385158</v>
+        <v>-0.4217658954850844</v>
       </c>
       <c r="G61">
-        <v>-5.600690152310625</v>
+        <v>-4.019469194001544</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>2.456696897913142</v>
       </c>
       <c r="E62">
-        <v>-11.71185511020179</v>
+        <v>-11.04255679878302</v>
       </c>
       <c r="F62">
-        <v>0.5933411992949166</v>
+        <v>-1.1075431037711</v>
       </c>
       <c r="G62">
-        <v>-5.566883620600299</v>
+        <v>-4.417124756396963</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>2.247926113082271</v>
       </c>
       <c r="E63">
-        <v>-11.48814653540123</v>
+        <v>-9.186852140313732</v>
       </c>
       <c r="F63">
-        <v>0.9632859395481618</v>
+        <v>-0.8830008653638491</v>
       </c>
       <c r="G63">
-        <v>-5.925276195089967</v>
+        <v>-5.02906501334178</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>2.06765119318977</v>
       </c>
       <c r="E64">
-        <v>-9.376471156560104</v>
+        <v>-10.31296631856172</v>
       </c>
       <c r="F64">
-        <v>-0.03982970870891358</v>
+        <v>-0.9718581799273466</v>
       </c>
       <c r="G64">
-        <v>-5.964463471402577</v>
+        <v>-4.885351355834767</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>1.915489306805752</v>
       </c>
       <c r="E65">
-        <v>-10.3914329401217</v>
+        <v>-10.11447604292551</v>
       </c>
       <c r="F65">
-        <v>0.8467992586316897</v>
+        <v>-1.138738591793127</v>
       </c>
       <c r="G65">
-        <v>-6.38611699807951</v>
+        <v>-4.773063230970984</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>1.787647294069924</v>
       </c>
       <c r="E66">
-        <v>-10.45107305474624</v>
+        <v>-9.731512579874398</v>
       </c>
       <c r="F66">
-        <v>0.4744240884186307</v>
+        <v>-1.022304098023031</v>
       </c>
       <c r="G66">
-        <v>-6.224548458313873</v>
+        <v>-5.082420800550362</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>1.684737627037822</v>
       </c>
       <c r="E67">
-        <v>-9.250446112119507</v>
+        <v>-9.603917621553014</v>
       </c>
       <c r="F67">
-        <v>0.9273778693716088</v>
+        <v>-1.307264141320866</v>
       </c>
       <c r="G67">
-        <v>-5.457214072561403</v>
+        <v>-5.491688954887054</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>1.603541238697015</v>
       </c>
       <c r="E68">
-        <v>-10.05189960789432</v>
+        <v>-8.747633429867815</v>
       </c>
       <c r="F68">
-        <v>0.3601027598930766</v>
+        <v>-1.039279002841198</v>
       </c>
       <c r="G68">
-        <v>-6.051698891170036</v>
+        <v>-5.625667145813805</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>1.546328341948586</v>
       </c>
       <c r="E69">
-        <v>-9.794221917667985</v>
+        <v>-9.396672376444071</v>
       </c>
       <c r="F69">
-        <v>-0.07373147303588615</v>
+        <v>-1.439309218796719</v>
       </c>
       <c r="G69">
-        <v>-6.278350682847536</v>
+        <v>-5.63102439371477</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>1.514355039280009</v>
       </c>
       <c r="E70">
-        <v>-8.611607452557031</v>
+        <v>-9.624563235048738</v>
       </c>
       <c r="F70">
-        <v>0.07813974985856961</v>
+        <v>-1.272841333897533</v>
       </c>
       <c r="G70">
-        <v>-6.579450467285223</v>
+        <v>-6.034961407596409</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>1.509106950385225</v>
       </c>
       <c r="E71">
-        <v>-8.000445793263212</v>
+        <v>-9.526244263356071</v>
       </c>
       <c r="F71">
-        <v>0.2022772321072979</v>
+        <v>-1.679704752558747</v>
       </c>
       <c r="G71">
-        <v>-6.541667771562631</v>
+        <v>-6.017156129485016</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>1.534228503112461</v>
       </c>
       <c r="E72">
-        <v>-10.74213841081288</v>
+        <v>-8.959418134954797</v>
       </c>
       <c r="F72">
-        <v>0.1178210335548743</v>
+        <v>-1.323780130597883</v>
       </c>
       <c r="G72">
-        <v>-6.267134924084114</v>
+        <v>-6.508396442493483</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>1.59027594710324</v>
       </c>
       <c r="E73">
-        <v>-9.871675155664711</v>
+        <v>-8.9157263518176</v>
       </c>
       <c r="F73">
-        <v>-0.1034035934041644</v>
+        <v>-1.7325678467358</v>
       </c>
       <c r="G73">
-        <v>-6.721234784539402</v>
+        <v>-5.939966854904161</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>1.679431178342597</v>
       </c>
       <c r="E74">
-        <v>-10.48551563626305</v>
+        <v>-9.72795327776902</v>
       </c>
       <c r="F74">
-        <v>-0.3477728055974214</v>
+        <v>-1.65408997572938</v>
       </c>
       <c r="G74">
-        <v>-6.759860750764924</v>
+        <v>-6.631213700293225</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>1.800587672170795</v>
       </c>
       <c r="E75">
-        <v>-9.904178187492819</v>
+        <v>-10.25561462337716</v>
       </c>
       <c r="F75">
-        <v>0.03684149299200026</v>
+        <v>-1.590738093498079</v>
       </c>
       <c r="G75">
-        <v>-6.440530136847493</v>
+        <v>-6.174469155567138</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>1.951718891671439</v>
       </c>
       <c r="E76">
-        <v>-10.5725254135182</v>
+        <v>-10.37384824337238</v>
       </c>
       <c r="F76">
-        <v>-0.552880716367593</v>
+        <v>-1.867184176629942</v>
       </c>
       <c r="G76">
-        <v>-6.474516809934606</v>
+        <v>-6.006814970159616</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>2.130326397024837</v>
       </c>
       <c r="E77">
-        <v>-10.95134812487846</v>
+        <v>-11.01992179706271</v>
       </c>
       <c r="F77">
-        <v>-0.1150065356151771</v>
+        <v>-1.947603740828523</v>
       </c>
       <c r="G77">
-        <v>-6.802066047824861</v>
+        <v>-5.850146797991499</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>2.329457631200813</v>
       </c>
       <c r="E78">
-        <v>-11.16063674995922</v>
+        <v>-9.795729533378896</v>
       </c>
       <c r="F78">
-        <v>-0.4685230935361026</v>
+        <v>-2.136302521716639</v>
       </c>
       <c r="G78">
-        <v>-5.904682641755265</v>
+        <v>-6.235142859864611</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>2.5452993636417</v>
       </c>
       <c r="E79">
-        <v>-12.20286436586832</v>
+        <v>-10.47235410957466</v>
       </c>
       <c r="F79">
-        <v>-1.118562046963139</v>
+        <v>-1.996717644140506</v>
       </c>
       <c r="G79">
-        <v>-5.98881388620389</v>
+        <v>-6.051764159784814</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>2.768499748146747</v>
       </c>
       <c r="E80">
-        <v>-11.87505970242226</v>
+        <v>-11.56528828254859</v>
       </c>
       <c r="F80">
-        <v>-0.7466764418851345</v>
+        <v>-2.143092649317387</v>
       </c>
       <c r="G80">
-        <v>-5.981548184006822</v>
+        <v>-6.371060834022559</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>2.990834415070234</v>
       </c>
       <c r="E81">
-        <v>-12.82217047257013</v>
+        <v>-11.59068932301124</v>
       </c>
       <c r="F81">
-        <v>-1.238585856689565</v>
+        <v>-2.215940107086979</v>
       </c>
       <c r="G81">
-        <v>-5.690510209223286</v>
+        <v>-5.795673612097921</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>3.200725828426209</v>
       </c>
       <c r="E82">
-        <v>-11.6801411885254</v>
+        <v>-12.72072413274987</v>
       </c>
       <c r="F82">
-        <v>-1.327219512054306</v>
+        <v>-2.248809725630063</v>
       </c>
       <c r="G82">
-        <v>-6.818085576635932</v>
+        <v>-6.058050832760214</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>3.386435262130675</v>
       </c>
       <c r="E83">
-        <v>-13.56700323835356</v>
+        <v>-13.51308209572331</v>
       </c>
       <c r="F83">
-        <v>-1.459429434643316</v>
+        <v>-2.53645119421076</v>
       </c>
       <c r="G83">
-        <v>-5.863853207094844</v>
+        <v>-5.665371349555456</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>3.535084827298841</v>
       </c>
       <c r="E84">
-        <v>-15.63987931699813</v>
+        <v>-14.58671214245943</v>
       </c>
       <c r="F84">
-        <v>-1.288965505393025</v>
+        <v>-2.74391995207891</v>
       </c>
       <c r="G84">
-        <v>-6.331006790505699</v>
+        <v>-6.133694546543131</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>3.634500527188791</v>
       </c>
       <c r="E85">
-        <v>-15.06143250330999</v>
+        <v>-15.56238454688815</v>
       </c>
       <c r="F85">
-        <v>-1.187543514063865</v>
+        <v>-2.908554659915701</v>
       </c>
       <c r="G85">
-        <v>-5.224915240333325</v>
+        <v>-6.259279193609453</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>3.673260091355815</v>
       </c>
       <c r="E86">
-        <v>-17.73791970305984</v>
+        <v>-16.36732674017582</v>
       </c>
       <c r="F86">
-        <v>-1.241950685079737</v>
+        <v>-2.887797429536351</v>
       </c>
       <c r="G86">
-        <v>-5.03563103598843</v>
+        <v>-5.74576922923879</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>3.642475589613879</v>
       </c>
       <c r="E87">
-        <v>-17.61995188858941</v>
+        <v>-17.57689139357359</v>
       </c>
       <c r="F87">
-        <v>-1.602703860631518</v>
+        <v>-2.968296517005601</v>
       </c>
       <c r="G87">
-        <v>-5.410082300458035</v>
+        <v>-5.559884214351524</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>3.533796007741924</v>
       </c>
       <c r="E88">
-        <v>-19.84211514830495</v>
+        <v>-18.84369975866147</v>
       </c>
       <c r="F88">
-        <v>-1.703485523958315</v>
+        <v>-2.806638961614472</v>
       </c>
       <c r="G88">
-        <v>-5.471283375162913</v>
+        <v>-5.860245158069925</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>3.340940630906721</v>
       </c>
       <c r="E89">
-        <v>-20.36883786815368</v>
+        <v>-20.2266069931236</v>
       </c>
       <c r="F89">
-        <v>-1.831474914630061</v>
+        <v>-3.20816852256906</v>
       </c>
       <c r="G89">
-        <v>-5.150824919582122</v>
+        <v>-5.701276919917038</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>3.062002230378421</v>
       </c>
       <c r="E90">
-        <v>-22.02953264207697</v>
+        <v>-22.46092670238691</v>
       </c>
       <c r="F90">
-        <v>-1.699823311670538</v>
+        <v>-3.473860740077779</v>
       </c>
       <c r="G90">
-        <v>-5.375576089197291</v>
+        <v>-5.675733394837585</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>2.693847407886274</v>
       </c>
       <c r="E91">
-        <v>-24.21546743940603</v>
+        <v>-23.54895593278622</v>
       </c>
       <c r="F91">
-        <v>-1.929126177541678</v>
+        <v>-3.68595178805355</v>
       </c>
       <c r="G91">
-        <v>-4.820106237758255</v>
+        <v>-5.760138767468278</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>2.24404846243804</v>
       </c>
       <c r="E92">
-        <v>-25.15817165233826</v>
+        <v>-25.11773598687973</v>
       </c>
       <c r="F92">
-        <v>-2.533632259939034</v>
+        <v>-3.528807178272873</v>
       </c>
       <c r="G92">
-        <v>-5.70735473332515</v>
+        <v>-5.331611150282943</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>1.713957826155774</v>
       </c>
       <c r="E93">
-        <v>-28.04423820196161</v>
+        <v>-26.30567902212044</v>
       </c>
       <c r="F93">
-        <v>-2.046436255656532</v>
+        <v>-3.613303138460631</v>
       </c>
       <c r="G93">
-        <v>-4.885009348293331</v>
+        <v>-5.714283649469964</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>1.11811812906772</v>
       </c>
       <c r="E94">
-        <v>-29.05693856195684</v>
+        <v>-28.0918423101668</v>
       </c>
       <c r="F94">
-        <v>-2.997618237962496</v>
+        <v>-3.583846393617081</v>
       </c>
       <c r="G94">
-        <v>-5.943885582535422</v>
+        <v>-5.846053150472634</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.4659130155921989</v>
       </c>
       <c r="E95">
-        <v>-32.07160722364785</v>
+        <v>-31.1705680267263</v>
       </c>
       <c r="F95">
-        <v>-2.60855560642004</v>
+        <v>-3.939380026163823</v>
       </c>
       <c r="G95">
-        <v>-5.408338323071171</v>
+        <v>-6.429826084023929</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.2275626609254721</v>
       </c>
       <c r="E96">
-        <v>-33.63213277023326</v>
+        <v>-33.05502536719737</v>
       </c>
       <c r="F96">
-        <v>-2.680303820646117</v>
+        <v>-3.732362728530198</v>
       </c>
       <c r="G96">
-        <v>-5.627176156187469</v>
+        <v>-6.341486319294429</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.9396121597788115</v>
       </c>
       <c r="E97">
-        <v>-35.93714844266781</v>
+        <v>-36.02200477985104</v>
       </c>
       <c r="F97">
-        <v>-2.858415237759052</v>
+        <v>-3.850680101406857</v>
       </c>
       <c r="G97">
-        <v>-4.307076650392356</v>
+        <v>-6.16905708202976</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.661159536614688</v>
       </c>
       <c r="E98">
-        <v>-38.54121401994097</v>
+        <v>-38.23039599081344</v>
       </c>
       <c r="F98">
-        <v>-2.578046834974935</v>
+        <v>-4.258763705252394</v>
       </c>
       <c r="G98">
-        <v>-5.717317334684838</v>
+        <v>-6.498600928787626</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.35507404619225</v>
       </c>
       <c r="E99">
-        <v>-41.00238628497773</v>
+        <v>-40.35296731956525</v>
       </c>
       <c r="F99">
-        <v>-2.901066218594393</v>
+        <v>-4.268311467937061</v>
       </c>
       <c r="G99">
-        <v>-6.023320097464635</v>
+        <v>-6.500754793075295</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.023367298211125</v>
       </c>
       <c r="E100">
-        <v>-41.77577237861936</v>
+        <v>-43.12427025725528</v>
       </c>
       <c r="F100">
-        <v>-2.867596862051682</v>
+        <v>-4.072994031500578</v>
       </c>
       <c r="G100">
-        <v>-5.57868157540754</v>
+        <v>-6.925632589322253</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.61027296092622</v>
       </c>
       <c r="E101">
-        <v>-44.87817970615303</v>
+        <v>-45.69628342612908</v>
       </c>
       <c r="F101">
-        <v>-2.968802649488712</v>
+        <v>-4.078472025135291</v>
       </c>
       <c r="G101">
-        <v>-6.371971983884858</v>
+        <v>-7.077400393892851</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.151446026047413</v>
       </c>
       <c r="E102">
-        <v>-47.15926457493391</v>
+        <v>-47.80698176200603</v>
       </c>
       <c r="F102">
-        <v>-3.322106316987118</v>
+        <v>-4.281309380854388</v>
       </c>
       <c r="G102">
-        <v>-7.733120226886046</v>
+        <v>-7.236462618851019</v>
       </c>
     </row>
   </sheetData>
